--- a/Results/Result_comparison_run_1-8.xlsx
+++ b/Results/Result_comparison_run_1-8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectglosac-my.sharepoint.com/personal/s4417653_glos_ac_uk/Documents/CT7004 Dissertation/_assignment/zip/Results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MEGA\FHM\CT7004 Dissertation\code\Olmo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="596" documentId="11_AD4DB114E441178AC67DF4360E16E392693EDF12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08FE96F6-73BF-A148-87D8-37A372D61FA9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E004D2-44F0-4195-8BB7-CEB5C57BCC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19180" yWindow="500" windowWidth="19220" windowHeight="22120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Classification" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="29">
   <si>
     <t>Model</t>
   </si>
@@ -123,6 +123,9 @@
   <si>
     <t>HC-Priority Performance:</t>
   </si>
+  <si>
+    <t>Olmo 3</t>
+  </si>
 </sst>
 </file>
 
@@ -191,7 +194,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -209,7 +212,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Prozent" xfId="1" builtinId="5"/>
@@ -1157,10 +1162,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5895DF17-9B1A-DE46-A4A3-ECFA54648784}" name="Tabelle7" displayName="Tabelle7" ref="A1:G8" totalsRowShown="0">
-  <autoFilter ref="A1:G8" xr:uid="{5895DF17-9B1A-DE46-A4A3-ECFA54648784}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G8">
-    <sortCondition descending="1" ref="B1:B8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5895DF17-9B1A-DE46-A4A3-ECFA54648784}" name="Tabelle7" displayName="Tabelle7" ref="A1:G9" totalsRowShown="0">
+  <autoFilter ref="A1:G9" xr:uid="{5895DF17-9B1A-DE46-A4A3-ECFA54648784}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G9">
+    <sortCondition ref="E1:E9"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{CEE7D533-1609-B44B-A5CA-8A01664B0977}" name="Model"/>
@@ -1178,10 +1183,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4A0BC20-A71F-D945-A46B-78FE22C3BEB5}" name="Tabelle1" displayName="Tabelle1" ref="A2:E9" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40" tableBorderDxfId="39">
-  <autoFilter ref="A2:E9" xr:uid="{C4A0BC20-A71F-D945-A46B-78FE22C3BEB5}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E9">
-    <sortCondition descending="1" ref="B2:B9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C4A0BC20-A71F-D945-A46B-78FE22C3BEB5}" name="Tabelle1" displayName="Tabelle1" ref="A2:E10" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40" tableBorderDxfId="39">
+  <autoFilter ref="A2:E10" xr:uid="{C4A0BC20-A71F-D945-A46B-78FE22C3BEB5}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E10">
+    <sortCondition descending="1" ref="B2:B10"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{100E8591-0102-5149-9CD1-8F24655E9BC7}" name="Model" dataDxfId="38"/>
@@ -1195,10 +1200,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F1A09EFD-290B-624F-BB13-B101E36B0436}" name="Tabelle2" displayName="Tabelle2" ref="A15:D22" totalsRowShown="0" headerRowDxfId="33" tableBorderDxfId="32">
-  <autoFilter ref="A15:D22" xr:uid="{F1A09EFD-290B-624F-BB13-B101E36B0436}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:D22">
-    <sortCondition descending="1" ref="B15:B22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F1A09EFD-290B-624F-BB13-B101E36B0436}" name="Tabelle2" displayName="Tabelle2" ref="A15:D23" totalsRowShown="0" headerRowDxfId="33" tableBorderDxfId="32">
+  <autoFilter ref="A15:D23" xr:uid="{F1A09EFD-290B-624F-BB13-B101E36B0436}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:D23">
+    <sortCondition descending="1" ref="B15:B23"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{1995C214-E033-1544-98B8-51B79F36F7CF}" name="Model" dataDxfId="31"/>
@@ -1211,10 +1216,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{43E8470D-5D56-2C4C-B4AC-54BA0316EB86}" name="Tabelle3" displayName="Tabelle3" ref="A25:D32" totalsRowShown="0" headerRowDxfId="27" tableBorderDxfId="26">
-  <autoFilter ref="A25:D32" xr:uid="{43E8470D-5D56-2C4C-B4AC-54BA0316EB86}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A26:D32">
-    <sortCondition descending="1" ref="B25:B32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{43E8470D-5D56-2C4C-B4AC-54BA0316EB86}" name="Tabelle3" displayName="Tabelle3" ref="A26:D34" totalsRowShown="0" headerRowDxfId="27" tableBorderDxfId="26">
+  <autoFilter ref="A26:D34" xr:uid="{43E8470D-5D56-2C4C-B4AC-54BA0316EB86}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A27:D34">
+    <sortCondition descending="1" ref="B26:B34"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{FAF6F9B8-04EC-F141-A151-3DC11614DCC7}" name="Model" dataDxfId="25"/>
@@ -1227,10 +1232,10 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1D974AB9-7BF5-6841-8B36-C4CA324749C9}" name="Tabelle4" displayName="Tabelle4" ref="A35:D42" totalsRowShown="0" headerRowDxfId="21" tableBorderDxfId="20">
-  <autoFilter ref="A35:D42" xr:uid="{1D974AB9-7BF5-6841-8B36-C4CA324749C9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A36:D42">
-    <sortCondition descending="1" ref="B35:B42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1D974AB9-7BF5-6841-8B36-C4CA324749C9}" name="Tabelle4" displayName="Tabelle4" ref="A37:D45" totalsRowShown="0" headerRowDxfId="21" tableBorderDxfId="20">
+  <autoFilter ref="A37:D45" xr:uid="{1D974AB9-7BF5-6841-8B36-C4CA324749C9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A38:D45">
+    <sortCondition descending="1" ref="B37:B45"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{5AB7F9F6-B2D9-4347-AA6F-131AD4C5BA8C}" name="Model" dataDxfId="19"/>
@@ -1243,10 +1248,10 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{47518F9A-EC99-9041-B0BD-927DE2F5B4BD}" name="Tabelle5" displayName="Tabelle5" ref="A45:D52" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
-  <autoFilter ref="A45:D52" xr:uid="{47518F9A-EC99-9041-B0BD-927DE2F5B4BD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A46:D52">
-    <sortCondition descending="1" ref="B45:B52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{47518F9A-EC99-9041-B0BD-927DE2F5B4BD}" name="Tabelle5" displayName="Tabelle5" ref="A48:D56" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" tableBorderDxfId="13">
+  <autoFilter ref="A48:D56" xr:uid="{47518F9A-EC99-9041-B0BD-927DE2F5B4BD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A49:D56">
+    <sortCondition descending="1" ref="B48:B56"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{339F53F6-5E52-934B-89D7-391A5A04E654}" name="Model" dataDxfId="12"/>
@@ -1259,10 +1264,10 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{43B2A9CE-A7E1-0141-97BC-5FEDE0B3D11A}" name="Tabelle6" displayName="Tabelle6" ref="A55:F62" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" tableBorderDxfId="6" dataCellStyle="Prozent">
-  <autoFilter ref="A55:F62" xr:uid="{43B2A9CE-A7E1-0141-97BC-5FEDE0B3D11A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A56:F62">
-    <sortCondition descending="1" ref="B55:B62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{43B2A9CE-A7E1-0141-97BC-5FEDE0B3D11A}" name="Tabelle6" displayName="Tabelle6" ref="A59:F67" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" tableBorderDxfId="6" dataCellStyle="Prozent">
+  <autoFilter ref="A59:F67" xr:uid="{43B2A9CE-A7E1-0141-97BC-5FEDE0B3D11A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A60:F67">
+    <sortCondition ref="F59:F67"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{58B1F0DA-E3D1-574F-A4D9-D3F93E803849}" name="Model" dataDxfId="5"/>
@@ -1277,10 +1282,10 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{FA1B13F6-A4A1-8443-A806-98608A6B9AB6}" name="Tabelle8" displayName="Tabelle8" ref="A1:C8" totalsRowShown="0">
-  <autoFilter ref="A1:C8" xr:uid="{FA1B13F6-A4A1-8443-A806-98608A6B9AB6}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C8">
-    <sortCondition ref="C1:C8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{FA1B13F6-A4A1-8443-A806-98608A6B9AB6}" name="Tabelle8" displayName="Tabelle8" ref="A1:C9" totalsRowShown="0">
+  <autoFilter ref="A1:C9" xr:uid="{FA1B13F6-A4A1-8443-A806-98608A6B9AB6}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C9">
+    <sortCondition descending="1" ref="C1:C9"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{6827F823-6D97-FD4A-BBEF-FE9A831FD54F}" name="Model"/>
@@ -1554,25 +1559,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
-    <col min="7" max="7" width="8.5" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.83203125" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" customWidth="1"/>
     <col min="14" max="14" width="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1595,172 +1600,196 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.55769230769230771</v>
+      </c>
+      <c r="C2" s="1">
+        <f>1-B2</f>
+        <v>0.44230769230769229</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.87878787878787878</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.68235294117647061</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.6966292134831461</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.1081081081081081</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.70192307692307687</v>
+      </c>
+      <c r="C3" s="1">
+        <f>1-B3</f>
+        <v>0.29807692307692313</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.76842105263157889</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.73366834170854267</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.702247191011236</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.29729729729729731</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.96153846153846201</v>
+      </c>
+      <c r="C4" s="1">
+        <f>1-B4</f>
+        <v>3.8461538461537992E-2</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.59880239520958101</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.73800738007380096</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.601123595505618</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.90540540540540504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.82692307692307687</v>
+      </c>
+      <c r="C5" s="1">
+        <f>1-B5</f>
+        <v>0.17307692307692313</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.67716535433070868</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.74458874458874458</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.6685393258426966</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.55405405405405406</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B6" s="1">
         <v>0.95192307692307687</v>
       </c>
-      <c r="C2" s="1">
-        <f t="shared" ref="C2:C8" si="0">1-B2</f>
+      <c r="C6" s="1">
+        <f>1-B6</f>
         <v>4.8076923076923128E-2</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D6" s="1">
         <v>0.6470588235294118</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E6" s="1">
         <v>0.77042801556420237</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.6685393258426966</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.72972972972972971</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.94230769230769229</v>
-      </c>
-      <c r="C3" s="1">
-        <f t="shared" si="0"/>
-        <v>5.7692307692307709E-2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.65333333333333332</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.77165354330708658</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0.6741573033707865</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.70270270270270274</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.93269230769230771</v>
-      </c>
-      <c r="C4" s="1">
-        <f t="shared" si="0"/>
-        <v>6.7307692307692291E-2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.79508196721311475</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.8584070796460177</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.8202247191011236</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.33783783783783777</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.92307692307692313</v>
-      </c>
-      <c r="C5" s="1">
-        <f t="shared" si="0"/>
-        <v>7.6923076923076872E-2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.70588235294117652</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.7303370786516854</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.54054054054054057</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.82692307692307687</v>
-      </c>
-      <c r="C6" s="1">
-        <f t="shared" si="0"/>
-        <v>0.17307692307692313</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.67716535433070868</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.74458874458874458</v>
       </c>
       <c r="F6" s="1">
         <v>0.6685393258426966</v>
       </c>
       <c r="G6" s="1">
-        <v>0.55405405405405406</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.72972972972972971</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B7" s="1">
-        <v>0.70192307692307687</v>
+        <v>0.94230769230769229</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" si="0"/>
-        <v>0.29807692307692313</v>
+        <f>1-B7</f>
+        <v>5.7692307692307709E-2</v>
       </c>
       <c r="D7" s="1">
-        <v>0.76842105263157889</v>
+        <v>0.65333333333333332</v>
       </c>
       <c r="E7" s="1">
-        <v>0.73366834170854267</v>
+        <v>0.77165354330708658</v>
       </c>
       <c r="F7" s="1">
-        <v>0.702247191011236</v>
+        <v>0.6741573033707865</v>
       </c>
       <c r="G7" s="1">
-        <v>0.29729729729729731</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>0.70270270270270274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1">
-        <v>0.55769230769230771</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" si="0"/>
-        <v>0.44230769230769229</v>
+        <f>1-B8</f>
+        <v>7.6923076923076872E-2</v>
       </c>
       <c r="D8" s="1">
-        <v>0.87878787878787878</v>
+        <v>0.70588235294117652</v>
       </c>
       <c r="E8" s="1">
-        <v>0.68235294117647061</v>
+        <v>0.8</v>
       </c>
       <c r="F8" s="1">
-        <v>0.6966292134831461</v>
+        <v>0.7303370786516854</v>
       </c>
       <c r="G8" s="1">
-        <v>0.1081081081081081</v>
+        <v>0.54054054054054057</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.93269230769230771</v>
+      </c>
+      <c r="C9" s="1">
+        <f>1-B9</f>
+        <v>6.7307692307692291E-2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.79508196721311475</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.8584070796460177</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.8202247191011236</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.33783783783783777</v>
       </c>
     </row>
   </sheetData>
@@ -1773,17 +1802,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A7F003-F7D8-4458-BD97-2E446EA6EA1B}">
-  <dimension ref="A1:F62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
-    <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -1792,7 +1821,7 @@
       <c r="E1" s="14"/>
       <c r="F1" s="14"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -1809,7 +1838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1826,7 +1855,7 @@
         <v>0.4943820224719101</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1843,7 +1872,7 @@
         <v>0.3651685393258427</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -1860,7 +1889,7 @@
         <v>0.3089887640449438</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1877,7 +1906,7 @@
         <v>0.37640449438202239</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>1</v>
       </c>
@@ -1894,46 +1923,63 @@
         <v>0.30337078651685401</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.31821078431372601</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.33455882352941202</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.154693432504527</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.185393258426966</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B9" s="2">
         <v>0.28522058823529423</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C9" s="2">
         <v>0.27039219034608369</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D9" s="1">
         <v>0.25829848779928971</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E9" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B10" s="10">
         <v>0.28492647058823528</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C10" s="10">
         <v>0.35555555555555551</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D10" s="7">
         <v>0.20340951319212189</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E10" s="7">
         <v>0.2247191011235955</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>0</v>
       </c>
@@ -1947,618 +1993,694 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6">
+        <v>6.6176470588235295E-2</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.12413793103448301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B17" s="7">
         <v>0.95</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C17" s="10">
         <v>0.13970588235294121</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D17" s="10">
         <v>0.24358974358974361</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B18" s="1">
         <v>0.94444444444444442</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C18" s="1">
         <v>0.25</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D18" s="1">
         <v>0.39534883720930231</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B19" s="1">
         <v>0.90384615384615385</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C19" s="2">
         <v>0.34558823529411759</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D19" s="2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B20" s="7">
         <v>0.8771929824561403</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C20" s="8">
         <v>0.36764705882352938</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D20" s="8">
         <v>0.51813471502590669</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B21" s="1">
         <v>0.85882352941176465</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C21" s="2">
         <v>0.53676470588235292</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D21" s="2">
         <v>0.66063348416289591</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B22" s="7">
         <v>0.8571428571428571</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C22" s="8">
         <v>0.26470588235294118</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D22" s="8">
         <v>0.4044943820224719</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B23" s="7">
         <v>0.82291666666666663</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C23" s="10">
         <v>0.58088235294117652</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D23" s="10">
         <v>0.68103448275862066</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B26" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B27" s="6">
         <v>0.25</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C27" s="5">
         <v>0.12</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D27" s="6">
         <v>0.1621621621621622</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B28" s="2">
         <v>0.25</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C28" s="1">
         <v>4.6875E-2</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D28" s="2">
         <v>7.8947368421052627E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="10">
+        <v>0.16666666666666699</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.125</v>
+      </c>
+      <c r="D29" s="10">
+        <v>0.14285714285714299</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B30" s="7">
         <v>0.16666666666666671</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C30" s="7">
         <v>3.125E-2</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D30" s="7">
         <v>5.2631578947368418E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B31" s="2">
         <v>0.16666666666666671</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C31" s="1">
         <v>5.7142857142857141E-2</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D31" s="2">
         <v>8.5106382978723402E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="8">
-        <v>0</v>
-      </c>
-      <c r="C30" s="7">
-        <v>0</v>
-      </c>
-      <c r="D30" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="2">
-        <v>0</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="10">
+      <c r="B32" s="8">
         <v>0</v>
       </c>
       <c r="C32" s="7">
         <v>0</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="10">
+        <v>0</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0</v>
+      </c>
+      <c r="D34" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="9" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B37" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C37" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D37" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="6">
+        <v>0.84</v>
+      </c>
+      <c r="C38" s="5">
+        <v>0.154411764705882</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.26086956521739102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B39" s="10">
         <v>0.8</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C39" s="7">
         <v>0.22222222222222221</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D39" s="10">
         <v>0.34782608695652167</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>1</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B40" s="1">
         <v>0.68</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C40" s="1">
         <v>0.22972972972972969</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D40" s="1">
         <v>0.34343434343434343</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B41" s="8">
         <v>0.68</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C41" s="7">
         <v>0.15315315315315309</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D41" s="8">
         <v>0.25</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>8</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B42" s="13">
         <v>0.56000000000000005</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C42" s="1">
         <v>0.24561403508771931</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D42" s="13">
         <v>0.34146341463414642</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B43" s="8">
         <v>0.52</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C43" s="7">
         <v>0.16455696202531639</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D43" s="8">
         <v>0.25</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B44" s="2">
         <v>0.48</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C44" s="1">
         <v>0.2181818181818182</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D44" s="2">
         <v>0.3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B45" s="10">
         <v>0.36</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C45" s="7">
         <v>0.1475409836065574</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D45" s="10">
         <v>0.20930232558139539</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="9" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B48" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C48" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D48" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B49" s="5">
         <v>0.4</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C49" s="5">
         <v>0.16666666666666671</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D49" s="5">
         <v>0.23529411764705879</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B50" s="7">
         <v>0.2</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C50" s="7">
         <v>0.33333333333333331</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D50" s="7">
         <v>0.25</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>1</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B51" s="1">
         <v>0.2</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C51" s="1">
         <v>0.25</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D51" s="1">
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B52" s="7">
         <v>0.2</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C52" s="7">
         <v>0.25</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D52" s="7">
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>8</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B53" s="1">
         <v>0.2</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C53" s="1">
         <v>0.2</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D53" s="1">
         <v>0.2</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B54" s="7">
         <v>0.2</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C54" s="7">
         <v>0.1111111111111111</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D54" s="7">
         <v>0.14285714285714279</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>6</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B55" s="1">
         <v>0.2</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C55" s="1">
         <v>5.8823529411764712E-2</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D55" s="1">
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>5.8823529411764698E-2</v>
+      </c>
+      <c r="D56" s="7">
+        <v>9.0909090909090898E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="9" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B59" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C59" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D59" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E59" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F59" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" s="17">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="C60" s="17">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="D60" s="17">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="E60" s="17">
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="F60" s="17">
+        <v>0.29729729729729731</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="8">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="D61" s="8">
+        <v>0.25806451612903231</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.34782608695652167</v>
+      </c>
+      <c r="F61" s="8">
+        <v>0.3108108108108108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0.38513513513513509</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" s="10">
+        <v>0.36666666666666659</v>
+      </c>
+      <c r="C63" s="10">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="D63" s="10">
+        <v>0.15714285714285711</v>
+      </c>
+      <c r="E63" s="10">
+        <v>0.22</v>
+      </c>
+      <c r="F63" s="10">
+        <v>0.39864864864864857</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B64" s="10">
         <v>0.83333333333333337</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C64" s="10">
         <v>0.16666666666666671</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D64" s="10">
         <v>0.26595744680851058</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E64" s="10">
         <v>0.40322580645161288</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F64" s="10">
         <v>0.46621621621621617</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="15" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="8">
+        <v>0.76666666666666672</v>
+      </c>
+      <c r="C65" s="8">
+        <v>0.23333333333333331</v>
+      </c>
+      <c r="D65" s="8">
+        <v>0.23958333333333329</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0.36507936507936511</v>
+      </c>
+      <c r="F65" s="8">
+        <v>0.49324324324324331</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>9</v>
       </c>
-      <c r="B57" s="13">
+      <c r="B66" s="13">
         <v>0.76666666666666672</v>
       </c>
-      <c r="C57" s="13">
+      <c r="C66" s="13">
         <v>0.23333333333333331</v>
       </c>
-      <c r="D57" s="13">
+      <c r="D66" s="13">
         <v>0.18699186991869921</v>
       </c>
-      <c r="E57" s="13">
+      <c r="E66" s="13">
         <v>0.30065359477124182</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F66" s="13">
         <v>0.67567567567567566</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="8">
-        <v>0.76666666666666672</v>
-      </c>
-      <c r="C58" s="8">
-        <v>0.23333333333333331</v>
-      </c>
-      <c r="D58" s="8">
-        <v>0.23958333333333329</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.36507936507936511</v>
-      </c>
-      <c r="F58" s="8">
-        <v>0.49324324324324331</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B67" s="10">
         <v>1</v>
       </c>
-      <c r="B59" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="C59" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="D59" s="1">
-        <v>0.26923076923076922</v>
-      </c>
-      <c r="E59" s="1">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="F59" s="1">
-        <v>0.38513513513513509</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B60" s="8">
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="C60" s="8">
-        <v>0.46666666666666667</v>
-      </c>
-      <c r="D60" s="8">
-        <v>0.25806451612903231</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.34782608695652167</v>
-      </c>
-      <c r="F60" s="8">
-        <v>0.3108108108108108</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>5</v>
-      </c>
-      <c r="B61" s="13">
-        <v>0.46666666666666667</v>
-      </c>
-      <c r="C61" s="13">
-        <v>0.53333333333333333</v>
-      </c>
-      <c r="D61" s="13">
-        <v>0.2413793103448276</v>
-      </c>
-      <c r="E61" s="13">
-        <v>0.31818181818181818</v>
-      </c>
-      <c r="F61" s="13">
-        <v>0.29729729729729731</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62" s="10">
-        <v>0.36666666666666659</v>
-      </c>
-      <c r="C62" s="10">
-        <v>0.6333333333333333</v>
-      </c>
-      <c r="D62" s="10">
-        <v>0.15714285714285711</v>
-      </c>
-      <c r="E62" s="10">
-        <v>0.22</v>
-      </c>
-      <c r="F62" s="10">
-        <v>0.39864864864864857</v>
+      <c r="C67" s="10">
+        <v>0</v>
+      </c>
+      <c r="D67" s="10">
+        <v>0.19607843137254899</v>
+      </c>
+      <c r="E67" s="10">
+        <v>0.32786885245901598</v>
+      </c>
+      <c r="F67" s="10">
+        <v>0.83108108108108103</v>
       </c>
     </row>
   </sheetData>
@@ -2579,15 +2701,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5076426-0C2D-BE42-A065-7923EB02B11F}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2598,43 +2720,43 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="11">
-        <v>1.8839999999999999</v>
+        <v>3.3511000000000002</v>
       </c>
       <c r="C2" s="12">
-        <f>0.008/178</f>
-        <v>4.4943820224719104E-5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <f>22.202/178</f>
+        <v>0.12473033707865169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B3" s="11">
-        <v>9.0292999999999992</v>
+        <v>2.9763000000000002</v>
       </c>
       <c r="C3" s="12">
-        <f>0.04/178</f>
-        <v>2.2471910112359551E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <f>0.91/178</f>
+        <v>5.1123595505617979E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" s="11">
-        <v>2.4325999999999999</v>
+        <v>3.4565000000000001</v>
       </c>
       <c r="C4" s="12">
-        <f>0.14/178</f>
-        <v>7.8651685393258438E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <f>0.773/178</f>
+        <v>4.3426966292134835E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2646,40 +2768,51 @@
         <v>9.5505617977528095E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="11">
-        <v>3.4565000000000001</v>
+        <v>2.4325999999999999</v>
       </c>
       <c r="C6" s="12">
-        <f>0.773/178</f>
-        <v>4.3426966292134835E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <f>0.14/178</f>
+        <v>7.8651685393258438E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11">
-        <v>2.9763000000000002</v>
+        <v>4.7271999999999998</v>
       </c>
       <c r="C7" s="12">
-        <f>0.91/178</f>
-        <v>5.1123595505617979E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>3.9982E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" s="11">
-        <v>3.3511000000000002</v>
+        <v>9.0292999999999992</v>
       </c>
       <c r="C8" s="12">
-        <f>22.202/178</f>
-        <v>0.12473033707865169</v>
+        <f>0.04/178</f>
+        <v>2.2471910112359551E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="11">
+        <v>1.8839999999999999</v>
+      </c>
+      <c r="C9" s="12">
+        <f>0.008/178</f>
+        <v>4.4943820224719104E-5</v>
       </c>
     </row>
   </sheetData>
